--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512469_ELIMINGRC14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512469_ELIMINGRC14FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0904</v>
+        <v>5.0275</v>
       </c>
       <c r="E2" t="n">
-        <v>8.777200000000001</v>
+        <v>10.0923</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.6867</v>
+        <v>-5.0649</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1798</v>
+        <v>2.2124</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3531</v>
+        <v>5.4009</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.1733</v>
+        <v>-3.1885</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9237</v>
+        <v>7.1755</v>
       </c>
       <c r="K2" t="n">
-        <v>6.918</v>
+        <v>7.1021</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0057</v>
+        <v>0.0733</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.744</v>
+        <v>-4.963</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.565</v>
+        <v>-1.7012</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.179</v>
+        <v>-3.2618</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0518</v>
+        <v>0.8461</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6044</v>
+        <v>0.2584</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6563</v>
+        <v>0.5877</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2592</v>
+        <v>3.3321</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6588</v>
+        <v>5.7742</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6006</v>
+        <v>1.0143</v>
       </c>
       <c r="E3" t="n">
-        <v>1.335</v>
+        <v>2.6107</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7343</v>
+        <v>-1.5964</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5416</v>
+        <v>-0.1422</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7572</v>
+        <v>-0.5594</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2156</v>
+        <v>0.4172</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7798</v>
+        <v>2.3616</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6998</v>
+        <v>-0.5003</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08</v>
+        <v>2.8619</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3214</v>
+        <v>-2.5038</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.457</v>
+        <v>-0.0591</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1356</v>
+        <v>-2.4447</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.7526</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5424</v>
+        <v>-0.2651</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3557</v>
+        <v>-0.0304</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1867</v>
+        <v>-0.2347</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5999</v>
+        <v>-0.3311</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>0.2795</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. KOHAN LOPEZ</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2894</v>
+        <v>0.3541</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0445</v>
+        <v>1.2028</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2449</v>
+        <v>-0.8487</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2443</v>
+        <v>-0.5887</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2443</v>
+        <v>-0.8026</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02</v>
+        <v>0.7995</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02</v>
+        <v>0.7184</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2643</v>
+        <v>-1.3881</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2643</v>
+        <v>-1.521</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.1329</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0451</v>
+        <v>0.3323</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0645</v>
+        <v>0.156</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0193</v>
+        <v>0.1763</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>T. KOHAN LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.344</v>
+        <v>-0.2726</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4659</v>
+        <v>-0.0413</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8099</v>
+        <v>-0.2313</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1784</v>
+        <v>-0.2571</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4835</v>
+        <v>-0.2571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3051</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.173</v>
+        <v>0.0205</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.518</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
-        <v>2.691</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3514</v>
+        <v>-0.2776</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0346</v>
+        <v>-0.2776</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3859</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8005</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8005</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.626</v>
+        <v>-0.0155</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9669</v>
+        <v>-0.0618</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6591</v>
+        <v>0.0464</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1051</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1316</v>
+        <v>0.2074</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9735</v>
+        <v>-1.0941</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3954</v>
+        <v>-1.4113</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6824</v>
+        <v>-0.6753</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.713</v>
+        <v>-0.736</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0618</v>
+        <v>0.0939</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0182</v>
+        <v>0.0129</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4572</v>
+        <v>-1.5052</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6642</v>
+        <v>-0.6882</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.793</v>
+        <v>-0.8171</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2903</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0067</v>
+        <v>0.3083</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2836</v>
+        <v>0.2164</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.197</v>
+        <v>-1.1382</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.098</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1241</v>
+        <v>-1.0402</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0129</v>
+        <v>-2.046</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2178</v>
+        <v>1.2187</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2308</v>
+        <v>-3.2648</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8234</v>
+        <v>0.9052</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2614</v>
+        <v>1.3266</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.438</v>
+        <v>-0.4213</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8363</v>
+        <v>-2.9512</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0436</v>
+        <v>-0.1078</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.7927</v>
+        <v>-2.8434</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2638</v>
+        <v>-0.1963</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1046</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3684</v>
+        <v>-0.1142</v>
       </c>
       <c r="V7" t="n">
-        <v>1.88</v>
+        <v>1.8832</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="8">
@@ -1033,55 +1033,55 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4728</v>
+        <v>-1.5218</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0089</v>
+        <v>-0.0021</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4638</v>
+        <v>-1.5197</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.744</v>
+        <v>-1.7876</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1997</v>
+        <v>-1.2316</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5443</v>
+        <v>-0.556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8639</v>
+        <v>-1.9092</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1997</v>
+        <v>-1.2316</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6643</v>
+        <v>-0.6776</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9836</v>
+        <v>-3.0933</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6985</v>
+        <v>1.8816</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.682</v>
+        <v>-4.9749</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4606</v>
+        <v>-4.4349</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1409</v>
+        <v>-2.0843</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3197</v>
+        <v>-2.3505</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5546</v>
+        <v>0.794</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1691</v>
+        <v>0.0156</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7237</v>
+        <v>0.7784</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.0152</v>
+        <v>-5.2288</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9718</v>
+        <v>-2.0999</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.0434</v>
+        <v>-3.1289</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7571</v>
+        <v>0.6142</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3651</v>
+        <v>0.1966</v>
       </c>
       <c r="U9" t="n">
-        <v>0.392</v>
+        <v>0.4176</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9791</v>
+        <v>2.0595</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3874</v>
+        <v>-4.1918</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7699</v>
+        <v>-3.3299</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3826</v>
+        <v>-0.8619</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.6596</v>
+        <v>-5.714</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.056</v>
+        <v>-4.0441</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6036</v>
+        <v>-1.6699</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7865</v>
+        <v>-2.6431</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.0265</v>
+        <v>-2.8863</v>
       </c>
       <c r="L10" t="n">
-        <v>0.24</v>
+        <v>0.2432</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.873</v>
+        <v>-3.0709</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0295</v>
+        <v>-1.1578</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8435</v>
+        <v>-1.9131</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2133</v>
+        <v>1.3585</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3584</v>
+        <v>0.4864</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8549</v>
+        <v>0.8721</v>
       </c>
       <c r="V10" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8376</v>
+        <v>-4.6245</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3803</v>
+        <v>-0.9134</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4573</v>
+        <v>-3.7111</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9749</v>
+        <v>-3.0392</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0638</v>
+        <v>-2.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9111</v>
+        <v>-0.9142</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1256</v>
+        <v>0.2054</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1218</v>
+        <v>0.1565</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1005</v>
+        <v>-3.2447</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1855</v>
+        <v>-2.2815</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9149</v>
+        <v>-0.9631</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2779</v>
+        <v>0.4984</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0243</v>
+        <v>0.2169</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3022</v>
+        <v>0.2815</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5221</v>
+        <v>-5.5728</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5001</v>
+        <v>1.5127</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.0222</v>
+        <v>-7.0855</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0331</v>
+        <v>-2.0679</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6193</v>
+        <v>-2.689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7892</v>
+        <v>1.928</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1761</v>
+        <v>-1.1443</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9653</v>
+        <v>3.0723</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.8223</v>
+        <v>-3.9959</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4432</v>
+        <v>-1.5447</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.3791</v>
+        <v>-2.4513</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2901</v>
+        <v>-0.2049</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2891</v>
+        <v>-0.4153</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.001</v>
+        <v>0.2104</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.448</v>
+        <v>-14.9057</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3686</v>
+        <v>13.1228</v>
       </c>
       <c r="F13" t="n">
-        <v>-25.8161</v>
+        <v>-28.0287</v>
       </c>
       <c r="G13" t="n">
-        <v>-19.065</v>
+        <v>-19.2765</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.6762</v>
+        <v>-7.848800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.3889</v>
+        <v>-11.4277</v>
       </c>
       <c r="J13" t="n">
-        <v>10.5846</v>
+        <v>11.7621</v>
       </c>
       <c r="K13" t="n">
-        <v>4.113099999999999</v>
+        <v>4.8217</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4715</v>
+        <v>6.9405</v>
       </c>
       <c r="M13" t="n">
-        <v>-29.6495</v>
+        <v>-31.0384</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.7892</v>
+        <v>-12.6704</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.8602</v>
+        <v>-18.3681</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.0042</v>
+        <v>-14.6052</v>
       </c>
       <c r="R13" t="n">
-        <v>13.0038</v>
+        <v>12.658</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7789</v>
+        <v>3.3687</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1124000000000001</v>
+        <v>0.9093000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6665</v>
+        <v>2.4595</v>
       </c>
       <c r="V13" t="n">
-        <v>2.8388</v>
+        <v>2.9494</v>
       </c>
       <c r="W13" t="n">
-        <v>14.676</v>
+        <v>15.057</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.837</v>
+        <v>-12.1074</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.9503</v>
+        <v>11.6276</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6135</v>
+        <v>12.6216</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6632</v>
+        <v>-0.994</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7723</v>
+        <v>10.8946</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6686</v>
+        <v>5.7185</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1037</v>
+        <v>5.1761</v>
       </c>
       <c r="J14" t="n">
-        <v>11.3033</v>
+        <v>11.597</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6984</v>
+        <v>5.85</v>
       </c>
       <c r="L14" t="n">
-        <v>5.6049</v>
+        <v>5.747</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.531</v>
+        <v>-0.7024</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0298</v>
+        <v>-0.1315</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5013</v>
+        <v>-0.571</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1626</v>
+        <v>-0.5455</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0891</v>
+        <v>-0.4439</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0736</v>
+        <v>-0.1015</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6593</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7787</v>
+        <v>2.2803</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5656</v>
+        <v>3.447</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7869</v>
+        <v>-1.1667</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1854</v>
+        <v>0.2833</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6126</v>
+        <v>-0.5028</v>
       </c>
       <c r="I15" t="n">
-        <v>0.798</v>
+        <v>0.7861</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6728</v>
+        <v>0.8832</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7689</v>
+        <v>-0.6002</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4417</v>
+        <v>1.4834</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4874</v>
+        <v>-0.5999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1563</v>
+        <v>0.0974</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6437</v>
+        <v>-0.6973</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9929</v>
+        <v>0.4391</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2335</v>
+        <v>-0.1578</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7594</v>
+        <v>0.5969</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.6593</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2604</v>
+        <v>1.4995</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2986</v>
+        <v>3.9782</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9618</v>
+        <v>-2.4787</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4868</v>
+        <v>0.7316</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2399</v>
+        <v>0.0313</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2468</v>
+        <v>0.7003</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7233</v>
+        <v>1.634</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9615</v>
+        <v>0.2233</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7618</v>
+        <v>1.4107</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2366</v>
+        <v>-0.9024</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7216</v>
+        <v>-0.192</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.515</v>
+        <v>-0.7104</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6002</v>
+        <v>1.7526</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4004</v>
+        <v>1.7526</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0134</v>
+        <v>-0.0432</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9759</v>
+        <v>-0.3775</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0375</v>
+        <v>0.3343</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3604</v>
+        <v>-0.9416</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5999</v>
+        <v>2.7216</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7605</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6312</v>
+        <v>1.4308</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6992</v>
+        <v>0.7458</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0679</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7199</v>
+        <v>0.4829</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0244</v>
+        <v>0.2463</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6955</v>
+        <v>0.2366</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4509</v>
+        <v>1.8131</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1254</v>
+        <v>1.0187</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3255</v>
+        <v>0.7944</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.731</v>
+        <v>-1.3302</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.101</v>
+        <v>-0.7723</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.63</v>
+        <v>-0.5578</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8005</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8005</v>
+        <v>1.3632</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0508</v>
+        <v>0.2079</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4111</v>
+        <v>0.2695</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4619</v>
+        <v>-0.0616</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.3242</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6593</v>
+        <v>0.6105</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.5993</v>
+        <v>0.7137</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8465</v>
+        <v>1.0992</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7159</v>
+        <v>3.9953</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8694</v>
+        <v>-2.8961</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1247</v>
+        <v>2.1153</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5413</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5666</v>
+        <v>1.574</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6392</v>
+        <v>3.71</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6795</v>
+        <v>1.7242</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9597</v>
+        <v>1.9858</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5146</v>
+        <v>-1.5947</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1215</v>
+        <v>-1.1829</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.678</v>
+        <v>-0.4319</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3223</v>
+        <v>-0.2095</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3557</v>
+        <v>-0.2224</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2941</v>
+        <v>0.9073</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3897</v>
+        <v>0.7257</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0955</v>
+        <v>0.1816</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9422</v>
+        <v>1.9542</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1335</v>
+        <v>1.1258</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8086</v>
+        <v>0.8284</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5214</v>
+        <v>2.595</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3196</v>
+        <v>1.3547</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2017</v>
+        <v>1.2402</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5792</v>
+        <v>-0.6407</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1861</v>
+        <v>-0.2289</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5677</v>
+        <v>0.0046</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4512</v>
+        <v>-0.2335</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1165</v>
+        <v>0.2381</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.171</v>
+        <v>-0.137</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7035</v>
+        <v>0.3364</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5324</v>
+        <v>-0.4734</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9131</v>
+        <v>-0.4732</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1797</v>
+        <v>-0.6353</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7335</v>
+        <v>0.1621</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5864</v>
+        <v>0.4517</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9449</v>
+        <v>-0.2616</v>
       </c>
       <c r="L20" t="n">
-        <v>2.6415</v>
+        <v>0.7134</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6733</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7652</v>
+        <v>-0.3736</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9081</v>
+        <v>-0.5513</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2006</v>
+        <v>0.7789</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0573</v>
+        <v>-0.4428</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4822</v>
+        <v>-0.1154</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5395</v>
+        <v>-0.3274</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.9994</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.5993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. VINALLONGA BLANCO</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0448</v>
+        <v>-0.1375</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3345</v>
+        <v>2.9054</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2897</v>
+        <v>-3.0428</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4711</v>
+        <v>2.9406</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6311</v>
+        <v>1.2111</v>
       </c>
       <c r="I21" t="n">
-        <v>0.16</v>
+        <v>1.7295</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3655</v>
+        <v>4.7904</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3163</v>
+        <v>2.0912</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6818</v>
+        <v>2.6992</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8366</v>
+        <v>-1.8498</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3148</v>
+        <v>-0.8802</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5218</v>
+        <v>-0.9697</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8002</v>
+        <v>2.1421</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2843</v>
+        <v>-0.2201</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.031</v>
+        <v>-0.5482</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2533</v>
+        <v>0.3281</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-3.0526</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8286</v>
+        <v>-0.6495</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0066</v>
+        <v>0.0187</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8351</v>
+        <v>-0.6682</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3216</v>
+        <v>-1.3734</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4729</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8486</v>
+        <v>-0.8689</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2</v>
+        <v>0.2042</v>
       </c>
       <c r="K22" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5215</v>
+        <v>-1.5776</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5929</v>
+        <v>-0.6276</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9286</v>
+        <v>-0.95</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3872</v>
+        <v>-0.1329</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1934</v>
+        <v>-0.1855</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1939</v>
+        <v>0.0526</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7008</v>
+        <v>-1.7321</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5106</v>
+        <v>-0.7452</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1902</v>
+        <v>-0.9869</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7134</v>
+        <v>1.7206</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5886</v>
+        <v>0.6168</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1248</v>
+        <v>1.1037</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1867</v>
+        <v>3.3599</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0251</v>
+        <v>1.147</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1616</v>
+        <v>2.2129</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4734</v>
+        <v>-1.6393</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4366</v>
+        <v>-0.5302</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0368</v>
+        <v>-1.1091</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.6007</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8134</v>
+        <v>-0.9211</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.4578</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9177</v>
+        <v>-0.4633</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.4476</v>
+        <v>16.1886</v>
       </c>
       <c r="E24" t="n">
-        <v>25.8165</v>
+        <v>28.0289</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.3685</v>
+        <v>-11.8402</v>
       </c>
       <c r="G24" t="n">
-        <v>19.0651</v>
+        <v>19.2765</v>
       </c>
       <c r="H24" t="n">
-        <v>7.6761</v>
+        <v>7.8485</v>
       </c>
       <c r="I24" t="n">
-        <v>11.3889</v>
+        <v>11.4279</v>
       </c>
       <c r="J24" t="n">
-        <v>29.6495</v>
+        <v>31.0385</v>
       </c>
       <c r="K24" t="n">
-        <v>11.7892</v>
+        <v>12.6705</v>
       </c>
       <c r="L24" t="n">
-        <v>17.8602</v>
+        <v>18.3681</v>
       </c>
       <c r="M24" t="n">
-        <v>-10.5846</v>
+        <v>-11.7619</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.1132</v>
+        <v>-4.8218</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.471500000000001</v>
+        <v>-6.9402</v>
       </c>
       <c r="P24" t="n">
-        <v>2.0007</v>
+        <v>1.9472</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.0038</v>
+        <v>-12.658</v>
       </c>
       <c r="R24" t="n">
-        <v>15.0043</v>
+        <v>14.6052</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.7788</v>
+        <v>-2.0859</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.6666</v>
+        <v>-2.4596</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1123999999999999</v>
+        <v>0.3738</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8388</v>
+        <v>-2.9495</v>
       </c>
       <c r="W24" t="n">
-        <v>11.837</v>
+        <v>12.1074</v>
       </c>
       <c r="X24" t="n">
-        <v>-14.6758</v>
+        <v>-15.057</v>
       </c>
     </row>
   </sheetData>
